--- a/01 지필평가 교과목별 학생답 정오표/지필평가 교과목별 학생답 정오표(10반).xlsx
+++ b/01 지필평가 교과목별 학생답 정오표/지필평가 교과목별 학생답 정오표(10반).xlsx
@@ -264,7 +264,7 @@
 ※ 기타란의 점수는 기타 점수와 기타2 점수가 합산된 점수입니다.</t>
   </si>
   <si>
-    <t>무원고등학교</t>
+    <t>oo고등학교</t>
   </si>
   <si>
     <t>/</t>
